--- a/MAJSushiConfig/ig/StructureDefinition-FRLMCorpsDocument.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMCorpsDocument.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMCorpsDocument</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMCorpsDocument</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -250,7 +250,7 @@
     <t>FRLMCorpsDocument.alerts</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMAlerts
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAlerts
 </t>
   </si>
   <si>
@@ -260,7 +260,7 @@
     <t>FRLMCorpsDocument.allergiesAndIntolerances</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMAllergiesAndIntolerances
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAllergiesAndIntolerances
 </t>
   </si>
   <si>
@@ -270,7 +270,7 @@
     <t>FRLMCorpsDocument.problems</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMProblems
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMProblems
 </t>
   </si>
   <si>
@@ -280,7 +280,7 @@
     <t>FRLMCorpsDocument.medicationSummary</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedicationSummary
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationSummary
 </t>
   </si>
   <si>
@@ -290,7 +290,7 @@
     <t>FRLMCorpsDocument.medicalDevicesAndImplants</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedicalDevicesAndImplants
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicalDevicesAndImplants
 </t>
   </si>
   <si>
@@ -300,7 +300,7 @@
     <t>FRLMCorpsDocument.procedures</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMProcedures
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMProcedures
 </t>
   </si>
   <si>
@@ -310,7 +310,7 @@
     <t>FRLMCorpsDocument.immunisations</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMImmunisations
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMImmunisations
 </t>
   </si>
   <si>
@@ -320,7 +320,7 @@
     <t>FRLMCorpsDocument.functionalStatus</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMFunctionalStatus
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMFunctionalStatus
 </t>
   </si>
   <si>
@@ -330,7 +330,7 @@
     <t>FRLMCorpsDocument.socialHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMSocialHistory
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSocialHistory
 </t>
   </si>
   <si>
@@ -340,7 +340,7 @@
     <t>FRLMCorpsDocument.pregnancyHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMSectionPregnancyHistory
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSectionPregnancyHistory
 </t>
   </si>
   <si>
@@ -350,7 +350,7 @@
     <t>FRLMCorpsDocument.advanceDirectives</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMAdvanceDirectives
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAdvanceDirectives
 </t>
   </si>
   <si>
@@ -360,7 +360,7 @@
     <t>FRLMCorpsDocument.observationResults</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMObservationResults
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMObservationResults
 </t>
   </si>
   <si>
@@ -370,7 +370,7 @@
     <t>FRLMCorpsDocument.carePlans</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMCarePlans
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMCarePlans
 </t>
   </si>
   <si>
@@ -380,7 +380,7 @@
     <t>FRLMCorpsDocument.familyMedicalHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMFamilyMedicalHistory
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMFamilyMedicalHistory
 </t>
   </si>
   <si>
@@ -390,7 +390,7 @@
     <t>FRLMCorpsDocument.historyOfPastIllness</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHistoryOfPastIllness
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHistoryOfPastIllness
 </t>
   </si>
   <si>
@@ -400,7 +400,7 @@
     <t>FRLMCorpsDocument.predictableAdverseDrugReactions</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPredictableAdverseDrugReaction
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPredictableAdverseDrugReaction
 </t>
   </si>
   <si>
@@ -410,7 +410,7 @@
     <t>FRLMCorpsDocument.hazardousWorkingConditions</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHazardousWorkingConditions
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHazardousWorkingConditions
 </t>
   </si>
   <si>
@@ -420,7 +420,7 @@
     <t>FRLMCorpsDocument.qrCode</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMQRCode
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMQRCode
 </t>
   </si>
   <si>
@@ -430,7 +430,7 @@
     <t>FRLMCorpsDocument.note</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMNote
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMNote
 </t>
   </si>
   <si>
@@ -440,7 +440,7 @@
     <t>FRLMCorpsDocument.medicationPrescriptions</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedicationPrescription
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationPrescription
 </t>
   </si>
   <si>
@@ -450,7 +450,7 @@
     <t>FRLMCorpsDocument.medicalDevicePrescriptions</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedicalDevicePrescriptions
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicalDevicePrescriptions
 </t>
   </si>
   <si>
@@ -460,7 +460,7 @@
     <t>FRLMCorpsDocument.presentedForm</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPresentedForm
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPresentedForm
 </t>
   </si>
   <si>
@@ -470,7 +470,7 @@
     <t>FRLMCorpsDocument.attachments</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMAttachments
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAttachments
 </t>
   </si>
   <si>
@@ -480,7 +480,7 @@
     <t>FRLMCorpsDocument.travelHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMSectionTravelHistory
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSectionTravelHistory
 </t>
   </si>
   <si>
@@ -490,7 +490,7 @@
     <t>FRLMCorpsDocument.patientStory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatientStory
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatientStory
 </t>
   </si>
   <si>
@@ -500,7 +500,7 @@
     <t>FRLMCorpsDocument.addendum</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMAddendum
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMAddendum
 </t>
   </si>
   <si>
@@ -510,7 +510,7 @@
     <t>FRLMCorpsDocument.vitalSigns</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMVitalSigns
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMVitalSigns
 </t>
   </si>
   <si>
@@ -520,7 +520,7 @@
     <t>FRLMCorpsDocument.resultData</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMResultData
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMResultData
 </t>
   </si>
   <si>
@@ -530,7 +530,7 @@
     <t>FRLMCorpsDocument.examinationReport</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMExaminationReport
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMExaminationReport
 </t>
   </si>
   <si>
@@ -540,7 +540,7 @@
     <t>FRLMCorpsDocument.orderInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrderInformation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrderInformation
 </t>
   </si>
   <si>
@@ -550,7 +550,7 @@
     <t>FRLMCorpsDocument.comparisonStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMComparisonStudy
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMComparisonStudy
 </t>
   </si>
   <si>
@@ -560,7 +560,7 @@
     <t>FRLMCorpsDocument.exposureInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMExposureInformation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMExposureInformation
 </t>
   </si>
   <si>
@@ -570,7 +570,7 @@
     <t>FRLMCorpsDocument.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMSupportingInformation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSupportingInformation
 </t>
   </si>
   <si>
@@ -580,7 +580,7 @@
     <t>FRLMCorpsDocument.dicomStudyMetadata</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDicomStudyMetadata
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDicomStudyMetadata
 </t>
   </si>
   <si>
@@ -590,7 +590,7 @@
     <t>FRLMCorpsDocument.recommendation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMRecommendation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMRecommendation
 </t>
   </si>
   <si>
@@ -600,7 +600,7 @@
     <t>FRLMCorpsDocument.conclusion</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMConclusion
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMConclusion
 </t>
   </si>
   <si>
@@ -610,7 +610,7 @@
     <t>FRLMCorpsDocument.medicationDispensations</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMMedicationDispensations
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMMedicationDispensations
 </t>
   </si>
   <si>
@@ -620,7 +620,7 @@
     <t>FRLMCorpsDocument.patientEducation</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatientEducation
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatientEducation
 </t>
   </si>
   <si>
@@ -630,7 +630,7 @@
     <t>FRLMCorpsDocument.patientHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatientHistory
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatientHistory
 </t>
   </si>
   <si>
@@ -640,7 +640,7 @@
     <t>FRLMCorpsDocument.reasonForReferral</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMReasonForReferral
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMReasonForReferral
 </t>
   </si>
   <si>
@@ -650,7 +650,7 @@
     <t>FRLMCorpsDocument.courseOfEncounter</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMCourseOfEncounter
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMCourseOfEncounter
 </t>
   </si>
   <si>
@@ -660,7 +660,7 @@
     <t>FRLMCorpsDocument.hospitalDischargeMedications</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHospitalDischargeMedications
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHospitalDischargeMedications
 </t>
   </si>
   <si>
@@ -979,7 +979,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="90.421875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="84.7265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/MAJSushiConfig/ig/StructureDefinition-FRLMCorpsDocument.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMCorpsDocument.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
